--- a/assumption_checking/BRZsel_atlas_results.xlsx
+++ b/assumption_checking/BRZsel_atlas_results.xlsx
@@ -1,319 +1,329 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\grant_2026\assumption_checking\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D2BEC1-1974-419E-8C41-DF12D3532282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="1170" yWindow="1185" windowWidth="21600" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CHN_RI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CHN_PR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="STH_RI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="STH_PR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CHN_RI" sheetId="1" r:id="rId1"/>
+    <sheet name="CHN_PR" sheetId="2" r:id="rId2"/>
+    <sheet name="STH_RI" sheetId="3" r:id="rId3"/>
+    <sheet name="STH_PR" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
-  <si>
-    <t xml:space="preserve">SPP: CHN ; release: RI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tagger A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tagger B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tagger C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 1: 240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 1: 211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 1: 232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 0 1:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 1 1 1 1 1 1:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 0 0:  22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 0:   2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 2 0 0 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 0 0:  21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 0 0:  26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 0 0:   6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 0 0:   7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 0 0:  13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 0 0 0 0:  28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 0 1 0 0 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 0 0 0 0 0:  21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 0 0 0 0 0:  16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 2 0 0 0 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0 0 0 0 0 0:   6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0 0 0 0 0 0:   5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 0 0 0 0:  30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0 0 0 0 0 0:   4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0 0 0 0 0 0:   2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0 0 0 0 0 0:   2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGGER A_est</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGGER A_se</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGGER B_est</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGGER B_se</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGGER C_est</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGGER C_se</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F_statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release to Crescent Bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crescent Bar to Sunland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunland to Wanapum BRZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wanapum BRZ to Mattawa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattawa to Priest BRZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priest BRZ to Lower Ringold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPP: CHN ; release: PR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1: 247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1: 243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1: 226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 1:   0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 0:   0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0:   3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0:   6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0:   5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0:  16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0:  25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0:  28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release to Lower Ringold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPP: STH ; release: RI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 1: 238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 1: 178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 1: 113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 0:   3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 1 0:   4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 0 1:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 1 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 0 0:  23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 0 0:  24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 1 0 0:  19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 0 0:  15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 0 0 0 0:  22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 0 1 0 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 0 0 0 0 0:  28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 1 0 0 0:  20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 0 0 0 0 0:  25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 1 0 0 0 0:  16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0 0 0 0 0 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0 0 0 0 0 0:   1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1 0 0 0 0 0:  36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0 0 0 0 0 0:   5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPP: STH ; release: PR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1: 224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 1: 132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0:   9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 0:   4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0:  26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 0:  36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total:  172</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="97">
+  <si>
+    <t>SPP: CHN ; release: RI</t>
+  </si>
+  <si>
+    <t>Tagger A</t>
+  </si>
+  <si>
+    <t>Tagger B</t>
+  </si>
+  <si>
+    <t>Tagger C</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 1: 240</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 1: 211</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 1: 232</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 0:   1</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 0 1:   1</t>
+  </si>
+  <si>
+    <t>0 1 1 1 1 1 1:   1</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 0 0:  22</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 0:   2</t>
+  </si>
+  <si>
+    <t>1 1 1 2 0 0 0:   1</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 0 0:  21</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 0 0:  26</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 0 0:   6</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 0 0:   7</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 0 0:  13</t>
+  </si>
+  <si>
+    <t>1 1 1 0 0 0 0:  28</t>
+  </si>
+  <si>
+    <t>1 1 0 1 0 0 0:   1</t>
+  </si>
+  <si>
+    <t>1 1 0 0 0 0 0:  21</t>
+  </si>
+  <si>
+    <t>1 1 0 0 0 0 0:  16</t>
+  </si>
+  <si>
+    <t>1 1 2 0 0 0 0:   1</t>
+  </si>
+  <si>
+    <t>1 0 0 0 0 0 0:   6</t>
+  </si>
+  <si>
+    <t>1 0 0 0 0 0 0:   5</t>
+  </si>
+  <si>
+    <t>1 1 1 0 0 0 0:  30</t>
+  </si>
+  <si>
+    <t>0 0 0 0 0 0 0:   4</t>
+  </si>
+  <si>
+    <t>0 0 0 0 0 0 0:   2</t>
+  </si>
+  <si>
+    <t>1 0 0 0 0 0 0:   2</t>
+  </si>
+  <si>
+    <t>Total:  329</t>
+  </si>
+  <si>
+    <t>Total:  293</t>
+  </si>
+  <si>
+    <t>Total:  331</t>
+  </si>
+  <si>
+    <t>reach</t>
+  </si>
+  <si>
+    <t>TAGGER A_est</t>
+  </si>
+  <si>
+    <t>TAGGER A_se</t>
+  </si>
+  <si>
+    <t>TAGGER B_est</t>
+  </si>
+  <si>
+    <t>TAGGER B_se</t>
+  </si>
+  <si>
+    <t>TAGGER C_est</t>
+  </si>
+  <si>
+    <t>TAGGER C_se</t>
+  </si>
+  <si>
+    <t>F_statistic</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>Release to Crescent Bar</t>
+  </si>
+  <si>
+    <t>Crescent Bar to Sunland</t>
+  </si>
+  <si>
+    <t>Sunland to Wanapum BRZ</t>
+  </si>
+  <si>
+    <t>Wanapum BRZ to Mattawa</t>
+  </si>
+  <si>
+    <t>Mattawa to Priest BRZ</t>
+  </si>
+  <si>
+    <t>Priest BRZ to Lower Ringold</t>
+  </si>
+  <si>
+    <t>Release to Lower Ringold</t>
+  </si>
+  <si>
+    <t>SPP: CHN ; release: PR</t>
+  </si>
+  <si>
+    <t>1 1: 247</t>
+  </si>
+  <si>
+    <t>1 1: 243</t>
+  </si>
+  <si>
+    <t>1 1: 226</t>
+  </si>
+  <si>
+    <t>0 1:   0</t>
+  </si>
+  <si>
+    <t>2 0:   0</t>
+  </si>
+  <si>
+    <t>1 0:   3</t>
+  </si>
+  <si>
+    <t>1 0:   6</t>
+  </si>
+  <si>
+    <t>1 0:   5</t>
+  </si>
+  <si>
+    <t>0 0:  16</t>
+  </si>
+  <si>
+    <t>0 0:  25</t>
+  </si>
+  <si>
+    <t>0 0:  28</t>
+  </si>
+  <si>
+    <t>Total:  266</t>
+  </si>
+  <si>
+    <t>Total:  274</t>
+  </si>
+  <si>
+    <t>Total:  259</t>
+  </si>
+  <si>
+    <t>SPP: STH ; release: RI</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 1: 238</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 1: 178</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 1: 113</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 0:   3</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 1 0:   4</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 0 1:   1</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 1 0:   1</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 0 0:  23</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 0 0:  24</t>
+  </si>
+  <si>
+    <t>1 1 1 1 1 0 0:  19</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 0 0:  15</t>
+  </si>
+  <si>
+    <t>1 1 1 0 0 0 0:  22</t>
+  </si>
+  <si>
+    <t>1 1 1 0 1 0 0:   1</t>
+  </si>
+  <si>
+    <t>1 1 0 0 0 0 0:  28</t>
+  </si>
+  <si>
+    <t>1 1 1 1 0 0 0:  20</t>
+  </si>
+  <si>
+    <t>1 1 0 0 0 0 0:  25</t>
+  </si>
+  <si>
+    <t>1 1 1 0 0 0 0:  16</t>
+  </si>
+  <si>
+    <t>1 0 0 0 0 0 0:   1</t>
+  </si>
+  <si>
+    <t>0 0 0 0 0 0 0:   1</t>
+  </si>
+  <si>
+    <t>1 1 0 0 0 0 0:  36</t>
+  </si>
+  <si>
+    <t>0 0 0 0 0 0 0:   5</t>
+  </si>
+  <si>
+    <t>Total:  332</t>
+  </si>
+  <si>
+    <t>Total:  282</t>
+  </si>
+  <si>
+    <t>Total:  211</t>
+  </si>
+  <si>
+    <t>SPP: STH ; release: PR</t>
+  </si>
+  <si>
+    <t>1 1: 224</t>
+  </si>
+  <si>
+    <t>1 1: 132</t>
+  </si>
+  <si>
+    <t>1 0:   9</t>
+  </si>
+  <si>
+    <t>1 0:   4</t>
+  </si>
+  <si>
+    <t>0 0:  26</t>
+  </si>
+  <si>
+    <t>0 0:  36</t>
+  </si>
+  <si>
+    <t>Total:  276</t>
+  </si>
+  <si>
+    <t>Total:  172</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -342,13 +352,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -630,11 +650,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -645,7 +668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -656,7 +679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -667,7 +690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -678,7 +701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -689,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -700,7 +723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -711,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -722,7 +745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -733,7 +756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -744,7 +767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -755,21 +778,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12"/>
-      <c r="B12"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13"/>
-      <c r="B13"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -780,7 +799,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -809,203 +828,261 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>41</v>
       </c>
-      <c r="B18" t="n">
-        <v>0.9878</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.006042</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.9932</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.00481</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.00426</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.438619811032503</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.644925926747936</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="B18">
+        <v>0.98780000000000001</v>
+      </c>
+      <c r="C18">
+        <v>6.0419999999999996E-3</v>
+      </c>
+      <c r="D18">
+        <v>0.99319999999999997</v>
+      </c>
+      <c r="E18">
+        <v>4.81E-3</v>
+      </c>
+      <c r="F18">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="G18">
+        <v>4.2599999999999999E-3</v>
+      </c>
+      <c r="H18">
+        <v>0.43861981103250303</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.64492592674793603</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="n">
-        <v>0.9815</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.007467</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.007618</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.9939</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.004298</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="B19">
+        <v>0.98150000000000004</v>
+      </c>
+      <c r="C19">
+        <v>7.4669999999999997E-3</v>
+      </c>
+      <c r="D19">
+        <v>0.98280000000000001</v>
+      </c>
+      <c r="E19">
+        <v>7.6179999999999998E-3</v>
+      </c>
+      <c r="F19">
+        <v>0.99390000000000001</v>
+      </c>
+      <c r="G19">
+        <v>4.2979999999999997E-3</v>
+      </c>
+      <c r="H19">
         <v>1.05343287826691</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.348738515007519</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="I19" s="1">
+        <v>0.34873851500751901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="n">
-        <v>0.9342</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.013885</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.9441</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.013589</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9361</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.013566</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.147482459106673</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.862877573832107</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="B20">
+        <v>0.93420000000000003</v>
+      </c>
+      <c r="C20">
+        <v>1.3885E-2</v>
+      </c>
+      <c r="D20">
+        <v>0.94410000000000005</v>
+      </c>
+      <c r="E20">
+        <v>1.3589E-2</v>
+      </c>
+      <c r="F20">
+        <v>0.93610000000000004</v>
+      </c>
+      <c r="G20">
+        <v>1.3566E-2</v>
+      </c>
+      <c r="H20">
+        <v>0.14748245910667299</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.86287757383210695</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.016902</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8963</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.018554</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9013</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.017105</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0765195334645568</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.92633481958373</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="B21">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="C21">
+        <v>1.6902E-2</v>
+      </c>
+      <c r="D21">
+        <v>0.89629999999999999</v>
+      </c>
+      <c r="E21">
+        <v>1.8554000000000001E-2</v>
+      </c>
+      <c r="F21">
+        <v>0.90129999999999999</v>
+      </c>
+      <c r="G21">
+        <v>1.7104999999999999E-2</v>
+      </c>
+      <c r="H21">
+        <v>7.6519533464556796E-2</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.92633481958372998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" t="n">
-        <v>0.9777</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.009004</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.010786</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9491</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.013255</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.82007825323368</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.162013072391005</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="B22">
+        <v>0.97770000000000001</v>
+      </c>
+      <c r="C22">
+        <v>9.0039999999999999E-3</v>
+      </c>
+      <c r="D22">
+        <v>0.97150000000000003</v>
+      </c>
+      <c r="E22">
+        <v>1.0786E-2</v>
+      </c>
+      <c r="F22">
+        <v>0.94910000000000005</v>
+      </c>
+      <c r="G22">
+        <v>1.3254999999999999E-2</v>
+      </c>
+      <c r="H22">
+        <v>1.8200782532336801</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.16201307239100499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>0.9163</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.017072</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="C23">
+        <v>1.7072E-2</v>
+      </c>
+      <c r="D23">
         <v>0.9103</v>
       </c>
-      <c r="E23" t="n">
-        <v>0.018685</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9004</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.018538</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.196506978873574</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.821595597463442</v>
+      <c r="E23">
+        <v>1.8685E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.90039999999999998</v>
+      </c>
+      <c r="G23">
+        <v>1.8537999999999999E-2</v>
+      </c>
+      <c r="H23">
+        <v>0.19650697887357399</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0.82159559746344202</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" t="s">
+        <v>39</v>
+      </c>
+      <c r="I25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.73519999999999996</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.4341999999999999E-2</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.73040000000000005</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2.5926000000000001E-2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.71230000000000004</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2.4915E-2</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.232056295235327</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0.79290148547453099</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1016,73 +1093,73 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1111,47 +1188,47 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.9398</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.014578</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9088</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.017396</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.8919</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.019295</v>
-      </c>
-      <c r="H12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>0.93979999999999997</v>
+      </c>
+      <c r="C12">
+        <v>1.4578000000000001E-2</v>
+      </c>
+      <c r="D12">
+        <v>0.90880000000000005</v>
+      </c>
+      <c r="E12">
+        <v>1.7395999999999998E-2</v>
+      </c>
+      <c r="F12">
+        <v>0.89190000000000003</v>
+      </c>
+      <c r="G12">
+        <v>1.9295E-2</v>
+      </c>
+      <c r="H12">
         <v>1.99508488457913</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>0.136002109195062</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>63</v>
       </c>
@@ -1162,7 +1239,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1173,7 +1250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1184,7 +1261,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1195,7 +1272,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>70</v>
       </c>
@@ -1206,7 +1283,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1217,7 +1294,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1228,7 +1305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -1239,7 +1316,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -1250,7 +1327,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -1261,23 +1338,20 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>84</v>
       </c>
-      <c r="B11"/>
       <c r="C11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12"/>
-      <c r="B12"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -1288,7 +1362,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1317,192 +1391,250 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="1">
         <v>0.9849</v>
       </c>
-      <c r="C17" t="n">
-        <v>0.006684</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.9965</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.00354</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9953</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.004728</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="C17" s="1">
+        <v>6.6839999999999998E-3</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.99650000000000005</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3.5400000000000002E-3</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.99529999999999996</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4.7280000000000004E-3</v>
+      </c>
+      <c r="H17" s="1">
         <v>1.5344116446359</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.215582492979973</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="I17" s="1">
+        <v>0.21558249297997301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
-      <c r="B18" t="n">
-        <v>0.9969</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.003053</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="B18" s="1">
+        <v>0.99690000000000001</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3.0530000000000002E-3</v>
+      </c>
+      <c r="D18" s="1">
         <v>0.9929</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.005015</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.9905</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.006702</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.395022723757758</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.673664730880782</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="E18" s="1">
+        <v>5.0150000000000004E-3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.99050000000000005</v>
+      </c>
+      <c r="G18" s="1">
+        <v>6.7019999999999996E-3</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.39502272375775799</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.67366473088078205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
-      <c r="B19" t="n">
-        <v>0.9233</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.014738</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.8996</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.017989</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.8269</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.026231</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6.16006570532773</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.00211211448999865</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="B19" s="1">
+        <v>0.92330000000000001</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.4737999999999999E-2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.89959999999999996</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1.7989000000000002E-2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.82689999999999997</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2.6231000000000001E-2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>6.1600657053277299</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2.1121144899986502E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="n">
-        <v>0.9269</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.015003</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.9124</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.017849</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.9078</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.022186</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.287780019366161</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.749926543411697</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="B20" s="1">
+        <v>0.92689999999999995</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.5003000000000001E-2</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.91239999999999999</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1.7849E-2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.90780000000000005</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2.2186000000000001E-2</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.28778001936616099</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.74992654341169696</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>45</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="1">
         <v>0.9466</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.013512</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="C21" s="1">
+        <v>1.3512E-2</v>
+      </c>
+      <c r="D21" s="1">
         <v>0.8952</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.020241</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E21" s="1">
+        <v>2.0240999999999999E-2</v>
+      </c>
+      <c r="F21" s="1">
         <v>0.871</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.026927</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G21" s="1">
+        <v>2.6927E-2</v>
+      </c>
+      <c r="H21" s="1">
         <v>3.39433638333275</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.0335628196299735</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="I21" s="1">
+        <v>3.3562819629973498E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>46</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="1">
         <v>0.9163</v>
       </c>
-      <c r="C22" t="n">
-        <v>0.017072</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.8878</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.022043</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.8531</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.030374</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.76789365712664</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="C22" s="1">
+        <v>1.7072E-2</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.88780000000000003</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2.2043E-2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.85309999999999997</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3.0374000000000002E-2</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1.7678936571266399</v>
+      </c>
+      <c r="I22" s="1">
         <v>0.170692146624465</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.72889999999999999</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.4396000000000001E-2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.64539999999999997</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2.8487999999999999E-2</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.54979999999999996</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3.4256000000000002E-2</v>
+      </c>
+      <c r="H25" s="1">
+        <v>9.3381009285707393</v>
+      </c>
+      <c r="I25" s="1">
+        <v>8.8006407945842794E-5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>88</v>
       </c>
@@ -1513,7 +1645,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1524,64 +1656,64 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>91</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
         <v>95</v>
@@ -1590,7 +1722,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1619,37 +1751,37 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.8996</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.018673</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8986</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.018174</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.7907</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.031019</v>
-      </c>
-      <c r="H12" t="n">
-        <v>7.16039634769925</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.000776746630459493</v>
+        <v>47</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.89959999999999996</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1.8672999999999999E-2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.89859999999999995</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.8173999999999999E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.79069999999999996</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3.1019000000000001E-2</v>
+      </c>
+      <c r="H12">
+        <v>7.1603963476992503</v>
+      </c>
+      <c r="I12" s="1">
+        <v>7.7674663045949302E-4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>